--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137172138</v>
+        <v>137193968</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>80457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>385</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511986</v>
+        <v>512159</v>
       </c>
       <c r="R2" t="n">
-        <v>7077577</v>
+        <v>7078147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På en gammal gran i luckig granskog.</t>
+          <t>På bark av en naturvärdesasp med 52 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,22 +778,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,13 +810,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172138</t>
+          <t>https://artportalen.se/Sighting/137193968</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137172139</v>
+        <v>137172138</v>
       </c>
       <c r="B3" t="n">
         <v>79485</v>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512047</v>
+        <v>511986</v>
       </c>
       <c r="R3" t="n">
-        <v>7077546</v>
+        <v>7077577</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,6 +892,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På en gammal gran i luckig granskog.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -917,9 +922,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,13 +946,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172139</t>
+          <t>https://artportalen.se/Sighting/137172138</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137172141</v>
+        <v>137172139</v>
       </c>
       <c r="B4" t="n">
         <v>79485</v>
@@ -980,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512109</v>
+        <v>512047</v>
       </c>
       <c r="R4" t="n">
-        <v>7077472</v>
+        <v>7077546</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1043,14 +1053,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1067,13 +1072,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172141</t>
+          <t>https://artportalen.se/Sighting/137172139</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137172142</v>
+        <v>137172141</v>
       </c>
       <c r="B5" t="n">
         <v>79485</v>
@@ -1111,10 +1116,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512094</v>
+        <v>512109</v>
       </c>
       <c r="R5" t="n">
-        <v>7077508</v>
+        <v>7077472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1198,13 +1203,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172142</t>
+          <t>https://artportalen.se/Sighting/137172141</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137172143</v>
+        <v>137172142</v>
       </c>
       <c r="B6" t="n">
         <v>79485</v>
@@ -1242,10 +1247,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512052</v>
+        <v>512094</v>
       </c>
       <c r="R6" t="n">
-        <v>7077469</v>
+        <v>7077508</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,11 +1285,6 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1334,13 +1334,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172143</t>
+          <t>https://artportalen.se/Sighting/137172142</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137172144</v>
+        <v>137172143</v>
       </c>
       <c r="B7" t="n">
         <v>79485</v>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512020</v>
+        <v>512052</v>
       </c>
       <c r="R7" t="n">
-        <v>7077461</v>
+        <v>7077469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Garnlav på en stående död gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1470,13 +1470,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172144</t>
+          <t>https://artportalen.se/Sighting/137172143</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137172145</v>
+        <v>137172144</v>
       </c>
       <c r="B8" t="n">
         <v>79485</v>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512108</v>
+        <v>512020</v>
       </c>
       <c r="R8" t="n">
-        <v>7077447</v>
+        <v>7077461</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1552,6 +1552,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Garnlav på en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1579,12 +1584,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1601,13 +1606,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172145</t>
+          <t>https://artportalen.se/Sighting/137172144</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137172146</v>
+        <v>137172145</v>
       </c>
       <c r="B9" t="n">
         <v>79485</v>
@@ -1645,10 +1650,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512142</v>
+        <v>512108</v>
       </c>
       <c r="R9" t="n">
-        <v>7077454</v>
+        <v>7077447</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1683,11 +1688,6 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1737,13 +1737,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172146</t>
+          <t>https://artportalen.se/Sighting/137172145</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137172148</v>
+        <v>137172146</v>
       </c>
       <c r="B10" t="n">
         <v>79485</v>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512141</v>
+        <v>512142</v>
       </c>
       <c r="R10" t="n">
-        <v>7077483</v>
+        <v>7077454</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1873,38 +1873,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172148</t>
+          <t>https://artportalen.se/Sighting/137172146</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137172120</v>
+        <v>137172148</v>
       </c>
       <c r="B11" t="n">
-        <v>80604</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512095</v>
+        <v>512141</v>
       </c>
       <c r="R11" t="n">
-        <v>7077507</v>
+        <v>7077483</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1955,6 +1955,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1970,6 +1975,26 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1984,48 +2009,43 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172120</t>
+          <t>https://artportalen.se/Sighting/137172148</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137172117</v>
+        <v>137193973</v>
       </c>
       <c r="B12" t="n">
-        <v>58005</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2033,10 +2053,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512059</v>
+        <v>512135</v>
       </c>
       <c r="R12" t="n">
-        <v>7077507</v>
+        <v>7078138</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2071,17 +2091,13 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i stambasen av en stående levande gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2100,14 +2116,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2124,48 +2135,43 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172117</t>
+          <t>https://artportalen.se/Sighting/137193973</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137172066</v>
+        <v>137193965</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>80494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2173,10 +2179,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512070</v>
+        <v>512059</v>
       </c>
       <c r="R13" t="n">
-        <v>7077539</v>
+        <v>7078108</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2211,43 +2217,39 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2264,48 +2266,43 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172066</t>
+          <t>https://artportalen.se/Sighting/137193965</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137172093</v>
+        <v>137172120</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>80604</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2313,10 +2310,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>512024</v>
+        <v>512095</v>
       </c>
       <c r="R14" t="n">
-        <v>7077581</v>
+        <v>7077507</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2351,48 +2348,19 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs 2 - 3 meter på stammen av en gran. Stående död ved indikerar ställvis medelhögt till mycket högt livsmiljövärde för tretåig hackspett i skogsbeståndet där fyndplatsen finns.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Äldre luckig och flerskiktad granskog med stor stamdiameterspridning.</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2409,33 +2377,33 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172093</t>
+          <t>https://artportalen.se/Sighting/137172120</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137172094</v>
+        <v>137172117</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2448,7 +2416,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2458,10 +2426,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>512030</v>
+        <v>512059</v>
       </c>
       <c r="R15" t="n">
-        <v>7077546</v>
+        <v>7077507</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2498,7 +2466,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran. Stående död ved av gran indikerar ställvis medelhögt till mycket högt livsmiljövärde för tretåig hackspett i skogsbeståndet där fyndplatsen finns.</t>
+          <t>Rejäla hackspår i stambasen av en stående levande gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2513,11 +2481,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Äldre luckig granskog med stor stamdiameterspridning.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2554,13 +2517,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172094</t>
+          <t>https://artportalen.se/Sighting/137172117</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137172095</v>
+        <v>137172066</v>
       </c>
       <c r="B16" t="n">
         <v>58008</v>
@@ -2593,7 +2556,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2603,10 +2566,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>512061</v>
+        <v>512070</v>
       </c>
       <c r="R16" t="n">
-        <v>7077497</v>
+        <v>7077539</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2643,7 +2606,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska, påtagligt tydliga på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2694,13 +2657,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172095</t>
+          <t>https://artportalen.se/Sighting/137172066</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137172096</v>
+        <v>137172093</v>
       </c>
       <c r="B17" t="n">
         <v>58008</v>
@@ -2743,10 +2706,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>512123</v>
+        <v>512024</v>
       </c>
       <c r="R17" t="n">
-        <v>7077445</v>
+        <v>7077581</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2783,7 +2746,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, längs 2 - 3 meter på stammen av en gran. Stående död ved indikerar ställvis medelhögt till mycket högt livsmiljövärde för tretåig hackspett i skogsbeståndet där fyndplatsen finns.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2798,6 +2761,11 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre luckig och flerskiktad granskog med stor stamdiameterspridning.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2834,13 +2802,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172096</t>
+          <t>https://artportalen.se/Sighting/137172093</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137172097</v>
+        <v>137172094</v>
       </c>
       <c r="B18" t="n">
         <v>58008</v>
@@ -2883,10 +2851,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>512166</v>
+        <v>512030</v>
       </c>
       <c r="R18" t="n">
-        <v>7077459</v>
+        <v>7077546</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2923,7 +2891,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran. Stående död ved av gran indikerar ställvis medelhögt till mycket högt livsmiljövärde för tretåig hackspett i skogsbeståndet där fyndplatsen finns.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2938,6 +2906,11 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre luckig granskog med stor stamdiameterspridning.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2974,13 +2947,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172097</t>
+          <t>https://artportalen.se/Sighting/137172094</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137172098</v>
+        <v>137172095</v>
       </c>
       <c r="B19" t="n">
         <v>58008</v>
@@ -3023,10 +2996,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512165</v>
+        <v>512061</v>
       </c>
       <c r="R19" t="n">
-        <v>7077456</v>
+        <v>7077497</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3063,7 +3036,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, påtagligt tydliga på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3114,13 +3087,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172098</t>
+          <t>https://artportalen.se/Sighting/137172095</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137172099</v>
+        <v>137172096</v>
       </c>
       <c r="B20" t="n">
         <v>58008</v>
@@ -3163,10 +3136,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512152</v>
+        <v>512123</v>
       </c>
       <c r="R20" t="n">
-        <v>7077455</v>
+        <v>7077445</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3254,13 +3227,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172099</t>
+          <t>https://artportalen.se/Sighting/137172096</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137172100</v>
+        <v>137172097</v>
       </c>
       <c r="B21" t="n">
         <v>58008</v>
@@ -3303,10 +3276,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512151</v>
+        <v>512166</v>
       </c>
       <c r="R21" t="n">
-        <v>7077453</v>
+        <v>7077459</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3343,7 +3316,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3394,13 +3367,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172100</t>
+          <t>https://artportalen.se/Sighting/137172097</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137172101</v>
+        <v>137172098</v>
       </c>
       <c r="B22" t="n">
         <v>58008</v>
@@ -3443,10 +3416,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512144</v>
+        <v>512165</v>
       </c>
       <c r="R22" t="n">
-        <v>7077450</v>
+        <v>7077456</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3534,13 +3507,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172101</t>
+          <t>https://artportalen.se/Sighting/137172098</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137172102</v>
+        <v>137172099</v>
       </c>
       <c r="B23" t="n">
         <v>58008</v>
@@ -3583,10 +3556,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>512132</v>
+        <v>512152</v>
       </c>
       <c r="R23" t="n">
-        <v>7077448</v>
+        <v>7077455</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3623,7 +3596,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3674,13 +3647,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172102</t>
+          <t>https://artportalen.se/Sighting/137172099</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137172103</v>
+        <v>137172100</v>
       </c>
       <c r="B24" t="n">
         <v>58008</v>
@@ -3713,7 +3686,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3723,10 +3696,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>512119</v>
+        <v>512151</v>
       </c>
       <c r="R24" t="n">
-        <v>7077451</v>
+        <v>7077453</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3763,7 +3736,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gammalt bohål med ca 45 mm i diameter och på 1,2 m höjd i en granhögstubbe. Ett getingbo inuti bohålet visar att det nyttjas av fler arter.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3792,12 +3765,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3814,13 +3787,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172103</t>
+          <t>https://artportalen.se/Sighting/137172100</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137172104</v>
+        <v>137172101</v>
       </c>
       <c r="B25" t="n">
         <v>58008</v>
@@ -3863,10 +3836,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>512155</v>
+        <v>512144</v>
       </c>
       <c r="R25" t="n">
-        <v>7077471</v>
+        <v>7077450</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3903,7 +3876,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3954,13 +3927,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172104</t>
+          <t>https://artportalen.se/Sighting/137172101</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137172105</v>
+        <v>137172102</v>
       </c>
       <c r="B26" t="n">
         <v>58008</v>
@@ -3993,7 +3966,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -4003,10 +3976,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>512161</v>
+        <v>512132</v>
       </c>
       <c r="R26" t="n">
-        <v>7077470</v>
+        <v>7077448</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4043,7 +4016,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av gran.</t>
+          <t>Ringhack, färska, längs flera meter på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4094,13 +4067,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172105</t>
+          <t>https://artportalen.se/Sighting/137172102</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137172106</v>
+        <v>137172103</v>
       </c>
       <c r="B27" t="n">
         <v>58008</v>
@@ -4133,7 +4106,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4143,10 +4116,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>512211</v>
+        <v>512119</v>
       </c>
       <c r="R27" t="n">
-        <v>7077481</v>
+        <v>7077451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4183,7 +4156,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Gammalt bohål med ca 45 mm i diameter och på 1,2 m höjd i en granhögstubbe. Ett getingbo inuti bohålet visar att det nyttjas av fler arter.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4212,12 +4185,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4234,13 +4207,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172106</t>
+          <t>https://artportalen.se/Sighting/137172103</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137172107</v>
+        <v>137172104</v>
       </c>
       <c r="B28" t="n">
         <v>58008</v>
@@ -4273,7 +4246,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4283,7 +4256,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>512221</v>
+        <v>512155</v>
       </c>
       <c r="R28" t="n">
         <v>7077471</v>
@@ -4323,7 +4296,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av gran vid en hyggeskant. Kring fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4374,13 +4347,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172107</t>
+          <t>https://artportalen.se/Sighting/137172104</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137172108</v>
+        <v>137172105</v>
       </c>
       <c r="B29" t="n">
         <v>58008</v>
@@ -4413,7 +4386,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4423,10 +4396,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>512172</v>
+        <v>512161</v>
       </c>
       <c r="R29" t="n">
-        <v>7077458</v>
+        <v>7077470</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4463,7 +4436,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på stambasen av gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4514,13 +4487,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172108</t>
+          <t>https://artportalen.se/Sighting/137172105</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137172109</v>
+        <v>137172106</v>
       </c>
       <c r="B30" t="n">
         <v>58008</v>
@@ -4553,7 +4526,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4563,10 +4536,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>512179</v>
+        <v>512211</v>
       </c>
       <c r="R30" t="n">
-        <v>7077464</v>
+        <v>7077481</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4603,7 +4576,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4654,13 +4627,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172109</t>
+          <t>https://artportalen.se/Sighting/137172106</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137172110</v>
+        <v>137172107</v>
       </c>
       <c r="B31" t="n">
         <v>58008</v>
@@ -4693,7 +4666,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4703,10 +4676,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>512177</v>
+        <v>512221</v>
       </c>
       <c r="R31" t="n">
-        <v>7077460</v>
+        <v>7077471</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4743,7 +4716,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs minst 7 meter på en gran vid en hyggeskant. Nära fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Ringhack, äldre, på stambasen av gran vid en hyggeskant. Kring fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4794,48 +4767,48 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137172110</t>
+          <t>https://artportalen.se/Sighting/137172107</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137172153</v>
+        <v>137172108</v>
       </c>
       <c r="B32" t="n">
-        <v>108397</v>
+        <v>58008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220083</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4843,10 +4816,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>512055</v>
+        <v>512172</v>
       </c>
       <c r="R32" t="n">
-        <v>7077541</v>
+        <v>7077458</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4881,13 +4854,17 @@
           <t>2026-10-09</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4896,9 +4873,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Fuktstråk i grandominerad äldre skog.</t>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4914,6 +4906,1493 @@
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137172108</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137172109</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Öster om Björnåflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>512179</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7077464</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran vid en hyggeskant.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137172109</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137172110</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Öster om Björnåflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>512177</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7077460</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 7 meter på en gran vid en hyggeskant. Nära fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137172110</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137193939</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Öster om Björnåflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>512039</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7078154</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137193939</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137193940</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Öster om Björnåflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>512018</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7078132</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137193940</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137193941</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Öster om Björnåflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>511997</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7078146</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137193941</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137193942</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Öster om Björnåflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>512089</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7078135</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på en gran. I skogsbeståndet kring fyndplatsen finns stående död ved som indikerar högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137193942</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137193946</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Öster om Björnåflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>512142</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7077739</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137193946</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137193947</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Öster om Björnåflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>512078</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7078133</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137193947</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137193949</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Öster om Björnåflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>512161</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7078145</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137193949</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137193950</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Öster om Björnåflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>512200</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7078105</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137193950</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137172153</v>
+      </c>
+      <c r="B43" t="n">
+        <v>108399</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Öster om Björnåflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>512055</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7077541</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Fuktstråk i grandominerad äldre skog.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137172153</t>
         </is>
@@ -4952,6 +6431,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193968</v>
       </c>
       <c r="B2" t="n">
-        <v>80457</v>
+        <v>80460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172138</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>137172139</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137172141</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137172142</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137172143</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137172144</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>137172145</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137172146</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>137172148</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137193973</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137193965</v>
       </c>
       <c r="B13" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>137172120</v>
       </c>
       <c r="B14" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193968</v>
       </c>
       <c r="B2" t="n">
-        <v>80460</v>
+        <v>80473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172138</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>137172139</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137172141</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137172142</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137172143</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137172144</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>137172145</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137172146</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>137172148</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137193973</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137193965</v>
       </c>
       <c r="B13" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>137172120</v>
       </c>
       <c r="B14" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>137172117</v>
       </c>
       <c r="B15" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>137172066</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>137172093</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137172094</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>137172095</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>137172096</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>137172097</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>137172098</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>137172099</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>137172100</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>137172101</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>137172102</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>137172103</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>137172104</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>137172105</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>137172106</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>137172107</v>
       </c>
       <c r="B31" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>137172108</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>137172109</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>137172110</v>
       </c>
       <c r="B34" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>137193939</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>137193940</v>
       </c>
       <c r="B36" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>137193941</v>
       </c>
       <c r="B37" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>137193942</v>
       </c>
       <c r="B38" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>137193946</v>
       </c>
       <c r="B39" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>137193947</v>
       </c>
       <c r="B40" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>137193949</v>
       </c>
       <c r="B41" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>137193950</v>
       </c>
       <c r="B42" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193968</v>
       </c>
       <c r="B2" t="n">
-        <v>80473</v>
+        <v>80475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172138</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>137172139</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137172141</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137172142</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137172143</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137172144</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>137172145</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137172146</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>137172148</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137193973</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137193965</v>
       </c>
       <c r="B13" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>137172120</v>
       </c>
       <c r="B14" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>137172117</v>
       </c>
       <c r="B15" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>137172066</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>137172093</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137172094</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         <v>137172095</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>137172096</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>137172097</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>137172098</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>137172099</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>137172100</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>137172101</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>137172102</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>137172103</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>137172104</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>137172105</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>137172106</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>137172107</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>137172108</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>137172109</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>137172110</v>
       </c>
       <c r="B34" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>137193939</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>137193940</v>
       </c>
       <c r="B36" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>137193941</v>
       </c>
       <c r="B37" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>137193942</v>
       </c>
       <c r="B38" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>137193946</v>
       </c>
       <c r="B39" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>137193947</v>
       </c>
       <c r="B40" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>137193949</v>
       </c>
       <c r="B41" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>137193950</v>
       </c>
       <c r="B42" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -2414,11 +2414,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2554,11 +2550,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2694,11 +2686,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2839,11 +2827,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2984,11 +2968,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3124,11 +3104,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3264,11 +3240,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3404,11 +3376,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3544,11 +3512,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3684,11 +3648,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3824,11 +3784,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3964,11 +3920,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4104,11 +4056,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4244,11 +4192,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4384,11 +4328,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4524,11 +4464,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4664,11 +4600,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4804,11 +4736,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4944,11 +4872,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -5084,11 +5008,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5224,11 +5144,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5364,11 +5280,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5504,11 +5416,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5644,11 +5552,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5784,11 +5688,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5924,11 +5824,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -6068,11 +5964,7 @@
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6191,11 +6083,7 @@
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6309,11 +6197,7 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -6170,7 +6170,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193968</v>
       </c>
       <c r="B2" t="n">
-        <v>80475</v>
+        <v>80485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172138</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>137172139</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137172141</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137172142</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137172143</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137172144</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>137172145</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137172146</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>137172148</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137193973</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137193965</v>
       </c>
       <c r="B13" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>137172120</v>
       </c>
       <c r="B14" t="n">
-        <v>80622</v>
+        <v>80632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>137172117</v>
       </c>
       <c r="B15" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>137172066</v>
       </c>
       <c r="B16" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137172093</v>
       </c>
       <c r="B17" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137172094</v>
       </c>
       <c r="B18" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>137172095</v>
       </c>
       <c r="B19" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>137172096</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>137172097</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>137172098</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>137172099</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>137172100</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137172101</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>137172102</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>137172103</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>137172104</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>137172105</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137172106</v>
       </c>
       <c r="B30" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>137172107</v>
       </c>
       <c r="B31" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137172108</v>
       </c>
       <c r="B32" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137172109</v>
       </c>
       <c r="B33" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137172110</v>
       </c>
       <c r="B34" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>137193939</v>
       </c>
       <c r="B35" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>137193940</v>
       </c>
       <c r="B36" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>137193941</v>
       </c>
       <c r="B37" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>137193942</v>
       </c>
       <c r="B38" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>137193946</v>
       </c>
       <c r="B39" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>137193947</v>
       </c>
       <c r="B40" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>137193949</v>
       </c>
       <c r="B41" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>137193950</v>
       </c>
       <c r="B42" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -6170,7 +6170,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193968</v>
       </c>
       <c r="B2" t="n">
-        <v>80485</v>
+        <v>80488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172138</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>137172139</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137172141</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137172142</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137172143</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137172144</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>137172145</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137172146</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>137172148</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137193973</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137193965</v>
       </c>
       <c r="B13" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>137172120</v>
       </c>
       <c r="B14" t="n">
-        <v>80632</v>
+        <v>80635</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>137172117</v>
       </c>
       <c r="B15" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>137172066</v>
       </c>
       <c r="B16" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137172093</v>
       </c>
       <c r="B17" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137172094</v>
       </c>
       <c r="B18" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>137172095</v>
       </c>
       <c r="B19" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>137172096</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>137172097</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>137172098</v>
       </c>
       <c r="B22" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>137172099</v>
       </c>
       <c r="B23" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>137172100</v>
       </c>
       <c r="B24" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137172101</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>137172102</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>137172103</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>137172104</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>137172105</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137172106</v>
       </c>
       <c r="B30" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>137172107</v>
       </c>
       <c r="B31" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137172108</v>
       </c>
       <c r="B32" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137172109</v>
       </c>
       <c r="B33" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137172110</v>
       </c>
       <c r="B34" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>137193939</v>
       </c>
       <c r="B35" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>137193940</v>
       </c>
       <c r="B36" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>137193941</v>
       </c>
       <c r="B37" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>137193942</v>
       </c>
       <c r="B38" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>137193946</v>
       </c>
       <c r="B39" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>137193947</v>
       </c>
       <c r="B40" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>137193949</v>
       </c>
       <c r="B41" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>137193950</v>
       </c>
       <c r="B42" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -6170,7 +6170,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193968</v>
       </c>
       <c r="B2" t="n">
-        <v>80488</v>
+        <v>80493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172138</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>137172139</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137172141</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137172142</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137172143</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137172144</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>137172145</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137172146</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>137172148</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137193973</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137193965</v>
       </c>
       <c r="B13" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>137172120</v>
       </c>
       <c r="B14" t="n">
-        <v>80635</v>
+        <v>80640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>137172117</v>
       </c>
       <c r="B15" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>137172066</v>
       </c>
       <c r="B16" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137172093</v>
       </c>
       <c r="B17" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137172094</v>
       </c>
       <c r="B18" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>137172095</v>
       </c>
       <c r="B19" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>137172096</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>137172097</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>137172098</v>
       </c>
       <c r="B22" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>137172099</v>
       </c>
       <c r="B23" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>137172100</v>
       </c>
       <c r="B24" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137172101</v>
       </c>
       <c r="B25" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>137172102</v>
       </c>
       <c r="B26" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>137172103</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>137172104</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>137172105</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137172106</v>
       </c>
       <c r="B30" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>137172107</v>
       </c>
       <c r="B31" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137172108</v>
       </c>
       <c r="B32" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137172109</v>
       </c>
       <c r="B33" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137172110</v>
       </c>
       <c r="B34" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>137193939</v>
       </c>
       <c r="B35" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>137193940</v>
       </c>
       <c r="B36" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>137193941</v>
       </c>
       <c r="B37" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>137193942</v>
       </c>
       <c r="B38" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>137193946</v>
       </c>
       <c r="B39" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>137193947</v>
       </c>
       <c r="B40" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>137193949</v>
       </c>
       <c r="B41" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>137193950</v>
       </c>
       <c r="B42" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -6170,7 +6170,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193968</v>
       </c>
       <c r="B2" t="n">
-        <v>80493</v>
+        <v>80504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172138</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>137172139</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137172141</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137172142</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137172143</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137172144</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>137172145</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137172146</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>137172148</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137193973</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137193965</v>
       </c>
       <c r="B13" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>137172120</v>
       </c>
       <c r="B14" t="n">
-        <v>80640</v>
+        <v>80651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193968</v>
       </c>
       <c r="B2" t="n">
-        <v>80504</v>
+        <v>80505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172138</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>137172139</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137172141</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137172142</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137172143</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137172144</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>137172145</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137172146</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>137172148</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137193973</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137193965</v>
       </c>
       <c r="B13" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>137172120</v>
       </c>
       <c r="B14" t="n">
-        <v>80651</v>
+        <v>80652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193968</v>
       </c>
       <c r="B2" t="n">
-        <v>80505</v>
+        <v>80507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172138</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>137172139</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137172141</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137172142</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137172143</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137172144</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>137172145</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137172146</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>137172148</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137193973</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137193965</v>
       </c>
       <c r="B13" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>137172120</v>
       </c>
       <c r="B14" t="n">
-        <v>80652</v>
+        <v>80654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 59072-2025 artfynd.xlsx
+++ b/artfynd/A 59072-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193968</v>
       </c>
       <c r="B2" t="n">
-        <v>80507</v>
+        <v>80511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>137172138</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>137172139</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137172141</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>137172142</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>137172143</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137172144</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>137172145</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>137172146</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>137172148</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>137193973</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137193965</v>
       </c>
       <c r="B13" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>137172120</v>
       </c>
       <c r="B14" t="n">
-        <v>80654</v>
+        <v>80658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>137172117</v>
       </c>
       <c r="B15" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>137172066</v>
       </c>
       <c r="B16" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         <v>137172093</v>
       </c>
       <c r="B17" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>137172094</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>137172095</v>
       </c>
       <c r="B19" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>137172096</v>
       </c>
       <c r="B20" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>137172097</v>
       </c>
       <c r="B21" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
         <v>137172098</v>
       </c>
       <c r="B22" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>137172099</v>
       </c>
       <c r="B23" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>137172100</v>
       </c>
       <c r="B24" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>137172101</v>
       </c>
       <c r="B25" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>137172102</v>
       </c>
       <c r="B26" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>137172103</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>137172104</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>137172105</v>
       </c>
       <c r="B29" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>137172106</v>
       </c>
       <c r="B30" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>137172107</v>
       </c>
       <c r="B31" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>137172108</v>
       </c>
       <c r="B32" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>137172109</v>
       </c>
       <c r="B33" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137172110</v>
       </c>
       <c r="B34" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>137193939</v>
       </c>
       <c r="B35" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>137193940</v>
       </c>
       <c r="B36" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>137193941</v>
       </c>
       <c r="B37" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>137193942</v>
       </c>
       <c r="B38" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>137193946</v>
       </c>
       <c r="B39" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>137193947</v>
       </c>
       <c r="B40" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>137193949</v>
       </c>
       <c r="B41" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>137193950</v>
       </c>
       <c r="B42" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>137172153</v>
       </c>
       <c r="B43" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
